--- a/btd mtg.xlsx
+++ b/btd mtg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Nicholas\Documents\wargame\wargame-tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB78F09-2A12-4E26-96A5-93E18F1D0640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5A2919-5E18-4012-9418-5258AADB5C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{0FBAB4E1-BC52-3645-BE0D-36FD61AE4D11}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Card list" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="686">
   <si>
     <t>Hive Courts</t>
   </si>
@@ -136,9 +137,6 @@
     <t>2G</t>
   </si>
   <si>
-    <t>Sporeborn;</t>
-  </si>
-  <si>
     <t>2B</t>
   </si>
   <si>
@@ -308,9 +306,6 @@
   </si>
   <si>
     <t>Sporeborn - Exile a card from an opponent's GY</t>
-  </si>
-  <si>
-    <t>CITP with 5 +1/+1 counters</t>
   </si>
   <si>
     <t>Rarity</t>
@@ -2075,31 +2070,37 @@
     <t>Striving Sprite</t>
   </si>
   <si>
-    <t>Reach</t>
-  </si>
-  <si>
     <t>Cowardice Sprite</t>
   </si>
   <si>
-    <t>Flying; 0: Untap ~ and remove it from combat</t>
-  </si>
-  <si>
-    <t>Lifelink; Flying</t>
-  </si>
-  <si>
     <t>Sacrificial Sprite</t>
   </si>
   <si>
-    <t>Sacrifice ~: Target player sacrifices a creature</t>
-  </si>
-  <si>
     <t>Vitriolic Sprite</t>
   </si>
   <si>
-    <t>Sacrifice ~: Deal 2 damage to target creature</t>
-  </si>
-  <si>
     <t>~ is each color of mana that was spent to cast it; Other Elementals you control get +1/+1 for each color they share with ~. ~ ETBs with half X +1/+1 counters on it, rounded down</t>
+  </si>
+  <si>
+    <t>Lifelink; Flying; Conjuration 1</t>
+  </si>
+  <si>
+    <t>Reach; Conjuration 1</t>
+  </si>
+  <si>
+    <t>Flying; 0: Untap ~ and remove it from combat; Conjuration 1</t>
+  </si>
+  <si>
+    <t>Conjuration 2</t>
+  </si>
+  <si>
+    <t>Sacrifice ~: Target player sacrifices a creature; Conjuration 1</t>
+  </si>
+  <si>
+    <t>Sacrifice ~: Deal 2 damage to target creature; Conjuration 1</t>
+  </si>
+  <si>
+    <t>~ CITP with 5 +1/+1 counters</t>
   </si>
 </sst>
 </file>
@@ -2767,7 +2768,7 @@
     </row>
     <row r="9" spans="1:16" ht="63" x14ac:dyDescent="0.25">
       <c r="J9" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>12</v>
@@ -2785,7 +2786,7 @@
         <v>15</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
@@ -2812,42 +2813,42 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B16" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B17" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B18" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -2894,131 +2895,131 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>551</v>
-      </c>
       <c r="H3" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>542</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>547</v>
-      </c>
       <c r="F12" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3038,15 +3039,15 @@
         <v>9</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="7" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="29" t="s">
         <v>100</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>102</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="29"/>
@@ -3055,174 +3056,174 @@
     </row>
     <row r="22" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>164</v>
-      </c>
       <c r="E22" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="189" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>222</v>
-      </c>
       <c r="E26" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>225</v>
-      </c>
       <c r="E27" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="E28" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>229</v>
-      </c>
       <c r="G28" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B29" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E29" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>231</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -3252,7 +3253,7 @@
         <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>24</v>
@@ -3267,62 +3268,62 @@
         <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J1">
         <f>SUM(L1,N1,P1,R1,T1,V1,X1)</f>
         <v>238</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L1" s="15">
         <f>COUNTIF($H:$H,"White")</f>
         <v>41</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N1" s="15">
         <f>COUNTIF($H:$H,"Black")</f>
         <v>41</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P1" s="15">
         <f>COUNTIF($H:$H,"Blue")</f>
         <v>41</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R1" s="15">
         <f>COUNTIF($H:$H,"Red")</f>
         <v>41</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="T1" s="15">
         <f>COUNTIF($H:$H,"Green")</f>
         <v>41</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="V1" s="15">
         <f>COUNTIF($H:$H,"Gold")</f>
         <v>14</v>
       </c>
       <c r="W1" s="15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="X1" s="16">
         <f>COUNTIF($H:$H,"Colorless")</f>
@@ -3352,7 +3353,7 @@
         <v>31</v>
       </c>
       <c r="Q2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R2">
         <f>COUNTIF($I:$I,Q2)</f>
@@ -3382,7 +3383,7 @@
     </row>
     <row r="3" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -3390,21 +3391,21 @@
       <c r="E3" s="1"/>
       <c r="F3" s="8"/>
       <c r="K3" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L3" s="20">
         <f>COUNTIF($G:$G,K3)</f>
         <v>109</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N3" s="20">
         <f>COUNTIF($G:$G,M3)</f>
         <v>69</v>
       </c>
       <c r="O3" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P3" s="20">
         <f>COUNTIF($G:$G,O3)</f>
@@ -3421,13 +3422,13 @@
     </row>
     <row r="4" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -3436,54 +3437,54 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L4" s="20">
         <f>COUNTIF($C:$C,"*Creature*")</f>
         <v>150</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N4" s="20">
         <f>COUNTIF($C:$C,"*Instant*")</f>
         <v>27</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P4" s="20">
         <f>COUNTIF($C:$C,"*Sorcery*")</f>
         <v>23</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R4" s="20">
         <f>COUNTIF($C:$C,"*Enchantment*")</f>
         <v>24</v>
       </c>
       <c r="S4" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="T4" s="20">
         <f>COUNTIF($C:$C,"*Artifact*")</f>
         <v>12</v>
       </c>
       <c r="U4" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="V4" s="20">
         <f>COUNTIF($C:$C,"*Land*")</f>
@@ -3494,25 +3495,25 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -3523,13 +3524,13 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3538,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>90</v>
+        <v>685</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
         <v>10</v>
@@ -3552,13 +3553,13 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -3567,10 +3568,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s">
         <v>10</v>
@@ -3581,13 +3582,13 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -3599,7 +3600,7 @@
         <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
         <v>10</v>
@@ -3610,25 +3611,25 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>127</v>
-      </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
@@ -3639,13 +3640,13 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -3654,10 +3655,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s">
         <v>10</v>
@@ -3668,13 +3669,13 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -3683,27 +3684,27 @@
         <v>2</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -3712,7 +3713,7 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
         <v>10</v>
@@ -3723,13 +3724,13 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" t="s">
         <v>129</v>
-      </c>
-      <c r="C13" t="s">
-        <v>131</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -3738,10 +3739,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s">
         <v>10</v>
@@ -3752,13 +3753,13 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
         <v>129</v>
-      </c>
-      <c r="C14" t="s">
-        <v>131</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -3767,10 +3768,10 @@
         <v>3</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
         <v>10</v>
@@ -3781,36 +3782,36 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s">
         <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -3819,7 +3820,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s">
         <v>10</v>
@@ -3830,13 +3831,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -3845,10 +3846,10 @@
         <v>2</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s">
         <v>10</v>
@@ -3859,19 +3860,19 @@
     </row>
     <row r="18" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s">
         <v>10</v>
@@ -3882,19 +3883,19 @@
     </row>
     <row r="19" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s">
         <v>10</v>
@@ -3905,42 +3906,42 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s">
         <v>10</v>
       </c>
       <c r="I20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s">
         <v>10</v>
@@ -3951,13 +3952,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3966,10 +3967,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s">
         <v>10</v>
@@ -3980,13 +3981,13 @@
     </row>
     <row r="23" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3995,10 +3996,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
         <v>10</v>
@@ -4009,13 +4010,13 @@
     </row>
     <row r="24" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -4024,10 +4025,10 @@
         <v>2</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
         <v>10</v>
@@ -4038,13 +4039,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -4053,27 +4054,27 @@
         <v>1</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
         <v>10</v>
       </c>
       <c r="I25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B26" t="s">
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -4082,10 +4083,10 @@
         <v>2</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
         <v>10</v>
@@ -4096,13 +4097,13 @@
     </row>
     <row r="27" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -4111,10 +4112,10 @@
         <v>2</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s">
         <v>10</v>
@@ -4125,13 +4126,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4140,10 +4141,10 @@
         <v>1</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s">
         <v>10</v>
@@ -4154,13 +4155,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -4169,10 +4170,10 @@
         <v>2</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s">
         <v>10</v>
@@ -4183,13 +4184,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -4198,10 +4199,10 @@
         <v>2</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
         <v>10</v>
@@ -4212,13 +4213,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4227,10 +4228,10 @@
         <v>5</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s">
         <v>10</v>
@@ -4241,36 +4242,36 @@
     </row>
     <row r="32" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s">
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s">
         <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B33" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D33">
         <v>6</v>
@@ -4279,10 +4280,10 @@
         <v>6</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s">
         <v>10</v>
@@ -4293,19 +4294,19 @@
     </row>
     <row r="34" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B34" t="s">
         <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s">
         <v>10</v>
@@ -4313,36 +4314,36 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C35" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s">
         <v>10</v>
       </c>
       <c r="I35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -4351,10 +4352,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s">
         <v>10</v>
@@ -4365,19 +4366,19 @@
     </row>
     <row r="37" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s">
         <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s">
         <v>10</v>
@@ -4388,13 +4389,13 @@
     </row>
     <row r="38" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
         <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4403,10 +4404,10 @@
         <v>3</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s">
         <v>10</v>
@@ -4417,19 +4418,19 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s">
         <v>10</v>
@@ -4440,13 +4441,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -4455,10 +4456,10 @@
         <v>4</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s">
         <v>10</v>
@@ -4469,13 +4470,13 @@
     </row>
     <row r="41" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B41" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C41" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -4484,10 +4485,10 @@
         <v>4</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G41" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s">
         <v>10</v>
@@ -4498,13 +4499,13 @@
     </row>
     <row r="42" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B42" t="s">
         <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -4513,10 +4514,10 @@
         <v>3</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G42" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s">
         <v>10</v>
@@ -4527,13 +4528,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C43" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -4542,27 +4543,27 @@
         <v>3</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s">
         <v>10</v>
       </c>
       <c r="I43" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
         <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -4571,10 +4572,10 @@
         <v>2</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G44" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s">
         <v>10</v>
@@ -4585,7 +4586,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4595,13 +4596,13 @@
     </row>
     <row r="46" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C46" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -4610,27 +4611,27 @@
         <v>2</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s">
         <v>7</v>
       </c>
       <c r="I46" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -4639,10 +4640,10 @@
         <v>2</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G47" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s">
         <v>7</v>
@@ -4653,13 +4654,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B48" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C48" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -4668,10 +4669,10 @@
         <v>2</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G48" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s">
         <v>7</v>
@@ -4682,13 +4683,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" t="s">
         <v>59</v>
-      </c>
-      <c r="B49" t="s">
-        <v>201</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -4700,7 +4701,7 @@
         <v>29</v>
       </c>
       <c r="G49" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s">
         <v>7</v>
@@ -4711,13 +4712,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -4726,27 +4727,27 @@
         <v>2</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="G50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s">
         <v>7</v>
       </c>
       <c r="I50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B51" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C51" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -4755,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G51" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s">
         <v>7</v>
@@ -4769,13 +4770,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B52" t="s">
         <v>31</v>
       </c>
       <c r="C52" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D52">
         <v>4</v>
@@ -4784,10 +4785,10 @@
         <v>3</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G52" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s">
         <v>7</v>
@@ -4798,13 +4799,13 @@
     </row>
     <row r="53" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -4813,10 +4814,10 @@
         <v>3</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G53" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s">
         <v>7</v>
@@ -4827,13 +4828,13 @@
     </row>
     <row r="54" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B54" t="s">
         <v>31</v>
       </c>
       <c r="C54" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -4842,10 +4843,10 @@
         <v>3</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G54" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s">
         <v>7</v>
@@ -4856,19 +4857,19 @@
     </row>
     <row r="55" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B55" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C55" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G55" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s">
         <v>7</v>
@@ -4876,13 +4877,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B56" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C56" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -4891,10 +4892,10 @@
         <v>1</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G56" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s">
         <v>7</v>
@@ -4905,13 +4906,13 @@
     </row>
     <row r="57" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C57" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -4920,10 +4921,10 @@
         <v>2</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G57" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s">
         <v>7</v>
@@ -4934,19 +4935,19 @@
     </row>
     <row r="58" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B58" t="s">
         <v>31</v>
       </c>
       <c r="C58" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G58" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s">
         <v>7</v>
@@ -4957,13 +4958,13 @@
     </row>
     <row r="59" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B59" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -4972,10 +4973,10 @@
         <v>2</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G59" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s">
         <v>7</v>
@@ -4986,13 +4987,13 @@
     </row>
     <row r="60" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -5001,10 +5002,10 @@
         <v>1</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G60" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s">
         <v>7</v>
@@ -5015,36 +5016,36 @@
     </row>
     <row r="61" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C61" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G61" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s">
         <v>7</v>
       </c>
       <c r="I61" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>514</v>
+      </c>
+      <c r="B62" t="s">
         <v>516</v>
       </c>
-      <c r="B62" t="s">
-        <v>518</v>
-      </c>
       <c r="C62" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D62">
         <v>6</v>
@@ -5053,10 +5054,10 @@
         <v>6</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G62" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s">
         <v>7</v>
@@ -5067,13 +5068,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B63" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C63" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -5082,10 +5083,10 @@
         <v>1</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G63" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s">
         <v>7</v>
@@ -5096,13 +5097,13 @@
     </row>
     <row r="64" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
         <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -5111,10 +5112,10 @@
         <v>2</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G64" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s">
         <v>7</v>
@@ -5125,25 +5126,25 @@
     </row>
     <row r="65" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>156</v>
+      </c>
+      <c r="B65" t="s">
+        <v>157</v>
+      </c>
+      <c r="C65" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B65" t="s">
-        <v>159</v>
-      </c>
-      <c r="C65" t="s">
-        <v>60</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="G65" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s">
         <v>7</v>
@@ -5154,19 +5155,19 @@
     </row>
     <row r="66" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s">
         <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s">
         <v>7</v>
@@ -5177,19 +5178,19 @@
     </row>
     <row r="67" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>501</v>
+      </c>
+      <c r="B67" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" t="s">
+        <v>206</v>
+      </c>
+      <c r="F67" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="B67" t="s">
-        <v>504</v>
-      </c>
-      <c r="C67" t="s">
-        <v>208</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>505</v>
-      </c>
       <c r="G67" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s">
         <v>7</v>
@@ -5200,13 +5201,13 @@
     </row>
     <row r="68" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B68" t="s">
         <v>31</v>
       </c>
       <c r="C68" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -5215,10 +5216,10 @@
         <v>2</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G68" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s">
         <v>7</v>
@@ -5229,13 +5230,13 @@
     </row>
     <row r="69" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -5244,10 +5245,10 @@
         <v>1</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G69" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s">
         <v>7</v>
@@ -5258,13 +5259,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B70" t="s">
         <v>31</v>
       </c>
       <c r="C70" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -5273,39 +5274,39 @@
         <v>4</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G70" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H70" t="s">
         <v>7</v>
       </c>
       <c r="I70" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>509</v>
+      </c>
+      <c r="B71" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" t="s">
+        <v>510</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="B71" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" t="s">
-        <v>512</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>513</v>
-      </c>
       <c r="G71" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s">
         <v>7</v>
@@ -5316,19 +5317,19 @@
     </row>
     <row r="72" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G72" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H72" t="s">
         <v>7</v>
@@ -5339,19 +5340,19 @@
     </row>
     <row r="73" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C73" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G73" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s">
         <v>7</v>
@@ -5362,19 +5363,19 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B74" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C74" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G74" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s">
         <v>7</v>
@@ -5385,36 +5386,36 @@
     </row>
     <row r="75" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B75" t="s">
         <v>31</v>
       </c>
       <c r="C75" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G75" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s">
         <v>7</v>
       </c>
       <c r="I75" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76" t="s">
         <v>31</v>
       </c>
       <c r="C76" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -5423,10 +5424,10 @@
         <v>2</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G76" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s">
         <v>7</v>
@@ -5437,13 +5438,13 @@
     </row>
     <row r="77" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C77" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -5452,10 +5453,10 @@
         <v>1</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G77" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H77" t="s">
         <v>7</v>
@@ -5466,13 +5467,13 @@
     </row>
     <row r="78" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" t="s">
         <v>39</v>
       </c>
-      <c r="B78" t="s">
-        <v>40</v>
-      </c>
       <c r="C78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -5481,10 +5482,10 @@
         <v>0</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G78" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H78" t="s">
         <v>7</v>
@@ -5495,13 +5496,13 @@
     </row>
     <row r="79" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -5510,10 +5511,10 @@
         <v>2</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G79" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H79" t="s">
         <v>7</v>
@@ -5524,13 +5525,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -5539,10 +5540,10 @@
         <v>3</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G80" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H80" t="s">
         <v>7</v>
@@ -5553,19 +5554,19 @@
     </row>
     <row r="81" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C81" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G81" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H81" t="s">
         <v>7</v>
@@ -5576,13 +5577,13 @@
     </row>
     <row r="82" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B82" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -5591,10 +5592,10 @@
         <v>0</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G82" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H82" t="s">
         <v>7</v>
@@ -5605,36 +5606,36 @@
     </row>
     <row r="83" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B83" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C83" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G83" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H83" t="s">
         <v>7</v>
       </c>
       <c r="I83" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C84" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D84">
         <v>4</v>
@@ -5643,27 +5644,27 @@
         <v>4</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G84" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H84" t="s">
         <v>7</v>
       </c>
       <c r="I84" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B85" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C85" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -5672,10 +5673,10 @@
         <v>5</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G85" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H85" t="s">
         <v>7</v>
@@ -5686,13 +5687,13 @@
     </row>
     <row r="86" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B86" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C86" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -5701,10 +5702,10 @@
         <v>3</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G86" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H86" t="s">
         <v>7</v>
@@ -5715,7 +5716,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
@@ -5725,42 +5726,42 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C89" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G89" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
       </c>
       <c r="I89" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B90" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C90" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G90" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -5771,19 +5772,19 @@
     </row>
     <row r="91" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G91" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -5794,19 +5795,19 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B92" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C92" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G92" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -5814,13 +5815,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B93" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -5829,10 +5830,10 @@
         <v>2</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G93" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -5843,19 +5844,19 @@
     </row>
     <row r="94" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C94" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G94" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -5866,13 +5867,13 @@
     </row>
     <row r="95" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C95" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -5881,27 +5882,27 @@
         <v>1</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G95" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
       </c>
       <c r="I95" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C96" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -5910,10 +5911,10 @@
         <v>1</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G96" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -5924,13 +5925,13 @@
     </row>
     <row r="97" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B97" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C97" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D97">
         <v>6</v>
@@ -5939,10 +5940,10 @@
         <v>6</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G97" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -5953,19 +5954,19 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B98" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C98" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G98" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -5976,19 +5977,19 @@
     </row>
     <row r="99" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B99" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C99" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G99" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -5996,13 +5997,13 @@
     </row>
     <row r="100" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B100" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C100" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -6011,10 +6012,10 @@
         <v>2</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G100" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -6025,13 +6026,13 @@
     </row>
     <row r="101" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B101" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C101" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D101">
         <v>6</v>
@@ -6040,10 +6041,10 @@
         <v>6</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G101" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -6054,19 +6055,19 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B102" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C102" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G102" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -6077,19 +6078,19 @@
     </row>
     <row r="103" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C103" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G103" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -6100,19 +6101,19 @@
     </row>
     <row r="104" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>381</v>
+      </c>
+      <c r="B104" t="s">
+        <v>382</v>
+      </c>
+      <c r="C104" t="s">
+        <v>148</v>
+      </c>
+      <c r="F104" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B104" t="s">
-        <v>384</v>
-      </c>
-      <c r="C104" t="s">
-        <v>150</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>385</v>
-      </c>
       <c r="G104" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -6120,19 +6121,19 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C105" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G105" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -6143,19 +6144,19 @@
     </row>
     <row r="106" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C106" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G106" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -6166,13 +6167,13 @@
     </row>
     <row r="107" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C107" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -6181,33 +6182,33 @@
         <v>1</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G107" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
       </c>
       <c r="I107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B108" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C108" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G108" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -6218,13 +6219,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B109" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C109" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -6233,10 +6234,10 @@
         <v>1</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G109" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -6247,13 +6248,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B110" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C110" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -6262,10 +6263,10 @@
         <v>1</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G110" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -6276,19 +6277,19 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C111" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G111" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -6299,13 +6300,13 @@
     </row>
     <row r="112" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B112" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C112" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -6314,10 +6315,10 @@
         <v>2</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G112" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -6328,13 +6329,13 @@
     </row>
     <row r="113" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B113" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C113" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D113">
         <v>3</v>
@@ -6343,10 +6344,10 @@
         <v>3</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G113" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -6357,13 +6358,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B114" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C114" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -6372,27 +6373,27 @@
         <v>1</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G114" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
       </c>
       <c r="I114" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B115" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C115" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -6401,33 +6402,33 @@
         <v>1</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G115" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
       </c>
       <c r="I115" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B116" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C116" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G116" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -6435,13 +6436,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B117" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C117" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -6450,10 +6451,10 @@
         <v>1</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G117" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -6464,19 +6465,19 @@
     </row>
     <row r="118" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B118" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C118" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G118" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -6487,13 +6488,13 @@
     </row>
     <row r="119" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B119" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C119" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -6502,10 +6503,10 @@
         <v>2</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G119" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -6516,42 +6517,42 @@
     </row>
     <row r="120" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B120" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C120" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G120" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
       </c>
       <c r="I120" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>445</v>
+      </c>
+      <c r="B121" t="s">
+        <v>446</v>
+      </c>
+      <c r="C121" t="s">
+        <v>148</v>
+      </c>
+      <c r="F121" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="B121" t="s">
-        <v>448</v>
-      </c>
-      <c r="C121" t="s">
-        <v>150</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>449</v>
-      </c>
       <c r="G121" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -6562,13 +6563,13 @@
     </row>
     <row r="122" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B122" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C122" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -6577,10 +6578,10 @@
         <v>1</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G122" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -6591,13 +6592,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B123" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C123" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -6606,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G123" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -6620,13 +6621,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B124" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C124" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -6635,10 +6636,10 @@
         <v>1</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G124" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -6649,25 +6650,25 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>552</v>
+      </c>
+      <c r="B125" t="s">
+        <v>267</v>
+      </c>
+      <c r="C125" t="s">
+        <v>553</v>
+      </c>
+      <c r="D125" t="s">
         <v>554</v>
       </c>
-      <c r="B125" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" t="s">
-        <v>555</v>
-      </c>
-      <c r="D125" t="s">
-        <v>556</v>
-      </c>
       <c r="E125" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G125" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -6678,19 +6679,19 @@
     </row>
     <row r="126" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G126" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -6701,13 +6702,13 @@
     </row>
     <row r="127" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B127" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C127" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -6716,10 +6717,10 @@
         <v>4</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G127" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -6730,13 +6731,13 @@
     </row>
     <row r="128" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B128" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -6745,44 +6746,44 @@
         <v>4</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G128" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B129" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C129" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G129" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -6792,13 +6793,13 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B131" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C131" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -6807,10 +6808,10 @@
         <v>1</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G131" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -6821,13 +6822,13 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B132" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -6836,10 +6837,10 @@
         <v>1</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G132" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -6850,19 +6851,19 @@
     </row>
     <row r="133" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B133" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G133" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -6870,13 +6871,13 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C134" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D134">
         <v>3</v>
@@ -6884,25 +6885,28 @@
       <c r="E134">
         <v>2</v>
       </c>
+      <c r="F134" s="7" t="s">
+        <v>682</v>
+      </c>
       <c r="G134" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
       </c>
       <c r="I134" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B135" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C135" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D135">
         <v>3</v>
@@ -6911,10 +6915,10 @@
         <v>2</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G135" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -6925,13 +6929,13 @@
     </row>
     <row r="136" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B136" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C136" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -6940,10 +6944,10 @@
         <v>2</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G136" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -6954,13 +6958,13 @@
     </row>
     <row r="137" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B137" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C137" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -6969,33 +6973,33 @@
         <v>1</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G137" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
       </c>
       <c r="I137" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B138" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G138" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -7003,13 +7007,13 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B139" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C139" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D139">
         <v>6</v>
@@ -7018,10 +7022,10 @@
         <v>6</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G139" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -7032,19 +7036,19 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B140" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C140" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G140" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -7052,19 +7056,19 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B141" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G141" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -7072,13 +7076,13 @@
     </row>
     <row r="142" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B142" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -7087,33 +7091,33 @@
         <v>1</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G142" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
       </c>
       <c r="I142" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>294</v>
+      </c>
+      <c r="B143" t="s">
+        <v>87</v>
+      </c>
+      <c r="C143" t="s">
+        <v>148</v>
+      </c>
+      <c r="F143" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B143" t="s">
-        <v>88</v>
-      </c>
-      <c r="C143" t="s">
-        <v>150</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>298</v>
-      </c>
       <c r="G143" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -7124,13 +7128,13 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B144" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -7139,10 +7143,10 @@
         <v>1</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G144" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -7153,13 +7157,13 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B145" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C145" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -7168,10 +7172,10 @@
         <v>1</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G145" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -7182,42 +7186,42 @@
     </row>
     <row r="146" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B146" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G146" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
       </c>
       <c r="I146" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>602</v>
+      </c>
+      <c r="B147" t="s">
+        <v>603</v>
+      </c>
+      <c r="C147" t="s">
+        <v>206</v>
+      </c>
+      <c r="F147" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="B147" t="s">
-        <v>605</v>
-      </c>
-      <c r="C147" t="s">
-        <v>208</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>606</v>
-      </c>
       <c r="G147" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -7225,19 +7229,19 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B148" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C148" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G148" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -7248,48 +7252,48 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B149" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C149" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G149" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
       </c>
       <c r="J149" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B150" t="s">
+        <v>87</v>
+      </c>
+      <c r="C150" t="s">
+        <v>59</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+      <c r="F150" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C150" t="s">
-        <v>60</v>
-      </c>
-      <c r="D150">
-        <v>1</v>
-      </c>
-      <c r="E150">
-        <v>1</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="G150" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -7300,13 +7304,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B151" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C151" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -7315,27 +7319,27 @@
         <v>2</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G151" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
       </c>
       <c r="I151" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B152" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C152" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -7344,10 +7348,10 @@
         <v>1</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G152" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -7358,13 +7362,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B153" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -7373,10 +7377,10 @@
         <v>1</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G153" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -7387,13 +7391,13 @@
     </row>
     <row r="154" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B154" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C154" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D154">
         <v>2</v>
@@ -7402,10 +7406,10 @@
         <v>2</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G154" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -7416,13 +7420,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B155" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C155" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D155">
         <v>3</v>
@@ -7431,10 +7435,10 @@
         <v>3</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G155" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -7445,13 +7449,13 @@
     </row>
     <row r="156" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>406</v>
+      </c>
+      <c r="B156" t="s">
+        <v>47</v>
+      </c>
+      <c r="C156" t="s">
         <v>408</v>
-      </c>
-      <c r="B156" t="s">
-        <v>48</v>
-      </c>
-      <c r="C156" t="s">
-        <v>410</v>
       </c>
       <c r="D156">
         <v>2</v>
@@ -7460,10 +7464,10 @@
         <v>2</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G156" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -7474,36 +7478,36 @@
     </row>
     <row r="157" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B157" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C157" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G157" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
       </c>
       <c r="I157" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B158" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C158" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -7512,10 +7516,10 @@
         <v>1</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G158" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -7526,13 +7530,13 @@
     </row>
     <row r="159" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B159" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C159" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -7541,10 +7545,10 @@
         <v>1</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G159" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -7555,13 +7559,13 @@
     </row>
     <row r="160" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B160" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C160" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D160">
         <v>2</v>
@@ -7570,10 +7574,10 @@
         <v>4</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G160" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -7584,13 +7588,13 @@
     </row>
     <row r="161" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B161" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C161" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D161">
         <v>2</v>
@@ -7599,10 +7603,10 @@
         <v>4</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G161" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -7613,19 +7617,19 @@
     </row>
     <row r="162" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B162" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C162" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G162" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -7636,36 +7640,36 @@
     </row>
     <row r="163" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B163" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C163" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G163" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
       </c>
       <c r="I163" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B164" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C164" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D164">
         <v>4</v>
@@ -7674,10 +7678,10 @@
         <v>4</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G164" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -7688,19 +7692,19 @@
     </row>
     <row r="165" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B165" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C165" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G165" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -7711,13 +7715,13 @@
     </row>
     <row r="166" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B166" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C166" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D166">
         <v>3</v>
@@ -7726,10 +7730,10 @@
         <v>3</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G166" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7740,13 +7744,13 @@
     </row>
     <row r="167" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B167" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C167" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -7755,10 +7759,10 @@
         <v>1</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G167" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -7769,13 +7773,13 @@
     </row>
     <row r="168" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B168" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C168" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D168">
         <v>2</v>
@@ -7784,10 +7788,10 @@
         <v>2</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G168" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7798,13 +7802,13 @@
     </row>
     <row r="169" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B169" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C169" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D169">
         <v>3</v>
@@ -7813,39 +7817,39 @@
         <v>3</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G169" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
       </c>
       <c r="I169" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="126" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>667</v>
+      </c>
+      <c r="B170" t="s">
+        <v>87</v>
+      </c>
+      <c r="C170" t="s">
+        <v>668</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="F170" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="B170" t="s">
-        <v>88</v>
-      </c>
-      <c r="C170" t="s">
-        <v>670</v>
-      </c>
-      <c r="D170">
-        <v>1</v>
-      </c>
-      <c r="E170">
-        <v>1</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>671</v>
-      </c>
       <c r="G170" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -7856,19 +7860,19 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B171" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C171" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G171" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -7879,7 +7883,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -7889,19 +7893,19 @@
     </row>
     <row r="173" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B173" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C173" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G173" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H173" t="s">
         <v>6</v>
@@ -7912,25 +7916,25 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B174" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C174" t="s">
+        <v>318</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="F174" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="D174">
-        <v>1</v>
-      </c>
-      <c r="E174">
-        <v>1</v>
-      </c>
-      <c r="F174" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="G174" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H174" t="s">
         <v>6</v>
@@ -7941,19 +7945,19 @@
     </row>
     <row r="175" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B175" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C175" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G175" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H175" t="s">
         <v>6</v>
@@ -7964,19 +7968,19 @@
     </row>
     <row r="176" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B176" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C176" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G176" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H176" t="s">
         <v>6</v>
@@ -7987,13 +7991,13 @@
     </row>
     <row r="177" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B177" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C177" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -8005,47 +8009,47 @@
         <v>684</v>
       </c>
       <c r="G177" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H177" t="s">
         <v>6</v>
       </c>
       <c r="I177" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>147</v>
+      </c>
+      <c r="B178" t="s">
+        <v>92</v>
+      </c>
+      <c r="C178" t="s">
+        <v>148</v>
+      </c>
+      <c r="F178" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B178" t="s">
-        <v>94</v>
-      </c>
-      <c r="C178" t="s">
-        <v>150</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>151</v>
-      </c>
       <c r="G178" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H178" t="s">
         <v>6</v>
       </c>
       <c r="I178" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B179" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C179" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D179">
         <v>2</v>
@@ -8054,10 +8058,10 @@
         <v>1</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G179" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H179" t="s">
         <v>6</v>
@@ -8068,13 +8072,13 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B180" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C180" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D180">
         <v>2</v>
@@ -8083,10 +8087,10 @@
         <v>1</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G180" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H180" t="s">
         <v>6</v>
@@ -8097,13 +8101,13 @@
     </row>
     <row r="181" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B181" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -8112,27 +8116,27 @@
         <v>1</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G181" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H181" t="s">
         <v>6</v>
       </c>
       <c r="I181" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B182" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C182" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D182">
         <v>4</v>
@@ -8141,10 +8145,10 @@
         <v>1</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G182" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H182" t="s">
         <v>6</v>
@@ -8155,13 +8159,13 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B183" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C183" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D183">
         <v>4</v>
@@ -8170,10 +8174,10 @@
         <v>2</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G183" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H183" t="s">
         <v>6</v>
@@ -8184,13 +8188,13 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B184" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D184">
         <v>3</v>
@@ -8199,10 +8203,10 @@
         <v>3</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G184" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H184" t="s">
         <v>6</v>
@@ -8213,59 +8217,59 @@
     </row>
     <row r="185" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B185" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C185" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G185" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H185" t="s">
         <v>6</v>
       </c>
       <c r="I185" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B186" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C186" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G186" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H186" t="s">
         <v>6</v>
       </c>
       <c r="I186" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B187" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C187" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -8274,33 +8278,33 @@
         <v>1</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G187" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H187" t="s">
         <v>6</v>
       </c>
       <c r="I187" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B188" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C188" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G188" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H188" t="s">
         <v>6</v>
@@ -8311,19 +8315,19 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B189" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C189" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G189" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H189" t="s">
         <v>6</v>
@@ -8334,25 +8338,25 @@
     </row>
     <row r="190" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>645</v>
+      </c>
+      <c r="B190" t="s">
+        <v>92</v>
+      </c>
+      <c r="C190" t="s">
+        <v>646</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="B190" t="s">
-        <v>94</v>
-      </c>
-      <c r="C190" t="s">
-        <v>648</v>
-      </c>
-      <c r="D190">
-        <v>1</v>
-      </c>
-      <c r="E190">
-        <v>1</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>649</v>
-      </c>
       <c r="G190" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H190" t="s">
         <v>6</v>
@@ -8363,19 +8367,19 @@
     </row>
     <row r="191" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B191" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C191" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="G191" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H191" t="s">
         <v>6</v>
@@ -8386,19 +8390,19 @@
     </row>
     <row r="192" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B192" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C192" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G192" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H192" t="s">
         <v>6</v>
@@ -8409,36 +8413,36 @@
     </row>
     <row r="193" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C193" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G193" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H193" t="s">
         <v>6</v>
       </c>
       <c r="I193" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B194" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C194" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -8447,27 +8451,27 @@
         <v>1</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G194" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H194" t="s">
         <v>6</v>
       </c>
       <c r="I194" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B195" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C195" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -8476,10 +8480,10 @@
         <v>1</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G195" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H195" t="s">
         <v>6</v>
@@ -8490,13 +8494,13 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B196" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C196" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D196">
         <v>5</v>
@@ -8505,10 +8509,10 @@
         <v>2</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G196" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H196" t="s">
         <v>6</v>
@@ -8519,13 +8523,13 @@
     </row>
     <row r="197" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B197" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C197" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D197">
         <v>3</v>
@@ -8534,10 +8538,10 @@
         <v>3</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G197" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H197" t="s">
         <v>6</v>
@@ -8548,13 +8552,13 @@
     </row>
     <row r="198" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B198" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C198" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -8563,10 +8567,10 @@
         <v>1</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G198" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H198" t="s">
         <v>6</v>
@@ -8577,13 +8581,13 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B199" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C199" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D199">
         <v>4</v>
@@ -8592,10 +8596,10 @@
         <v>3</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G199" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H199" t="s">
         <v>6</v>
@@ -8606,13 +8610,13 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B200" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C200" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D200">
         <v>5</v>
@@ -8621,10 +8625,10 @@
         <v>2</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G200" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H200" t="s">
         <v>6</v>
@@ -8635,19 +8639,19 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B201" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C201" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G201" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H201" t="s">
         <v>6</v>
@@ -8655,13 +8659,13 @@
     </row>
     <row r="202" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B202" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C202" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D202">
         <v>3</v>
@@ -8670,10 +8674,10 @@
         <v>2</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G202" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H202" t="s">
         <v>6</v>
@@ -8684,13 +8688,13 @@
     </row>
     <row r="203" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B203" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C203" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D203">
         <v>2</v>
@@ -8699,10 +8703,10 @@
         <v>2</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G203" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H203" t="s">
         <v>6</v>
@@ -8713,36 +8717,36 @@
     </row>
     <row r="204" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B204" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C204" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G204" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H204" t="s">
         <v>6</v>
       </c>
       <c r="I204" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="205" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B205" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C205" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D205">
         <v>2</v>
@@ -8751,10 +8755,10 @@
         <v>2</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G205" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H205" t="s">
         <v>6</v>
@@ -8765,13 +8769,13 @@
     </row>
     <row r="206" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B206" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C206" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -8780,10 +8784,10 @@
         <v>1</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G206" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H206" t="s">
         <v>6</v>
@@ -8794,19 +8798,19 @@
     </row>
     <row r="207" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B207" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C207" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G207" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H207" t="s">
         <v>6</v>
@@ -8817,25 +8821,25 @@
     </row>
     <row r="208" spans="1:9" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>478</v>
+      </c>
+      <c r="B208" t="s">
+        <v>479</v>
+      </c>
+      <c r="C208" t="s">
+        <v>408</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="B208" t="s">
-        <v>481</v>
-      </c>
-      <c r="C208" t="s">
-        <v>410</v>
-      </c>
-      <c r="D208">
-        <v>1</v>
-      </c>
-      <c r="E208">
-        <v>1</v>
-      </c>
-      <c r="F208" s="7" t="s">
-        <v>482</v>
-      </c>
       <c r="G208" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H208" t="s">
         <v>6</v>
@@ -8846,19 +8850,19 @@
     </row>
     <row r="209" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>205</v>
+      </c>
+      <c r="B209" t="s">
+        <v>190</v>
+      </c>
+      <c r="C209" t="s">
+        <v>206</v>
+      </c>
+      <c r="F209" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B209" t="s">
-        <v>192</v>
-      </c>
-      <c r="C209" t="s">
-        <v>208</v>
-      </c>
-      <c r="F209" s="7" t="s">
-        <v>209</v>
-      </c>
       <c r="G209" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H209" t="s">
         <v>6</v>
@@ -8866,13 +8870,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B210" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C210" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D210">
         <v>3</v>
@@ -8881,10 +8885,10 @@
         <v>3</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G210" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H210" t="s">
         <v>6</v>
@@ -8895,13 +8899,13 @@
     </row>
     <row r="211" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B211" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C211" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D211">
         <v>3</v>
@@ -8910,10 +8914,10 @@
         <v>2</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G211" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H211" t="s">
         <v>6</v>
@@ -8924,13 +8928,13 @@
     </row>
     <row r="212" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B212" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C212" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D212">
         <v>3</v>
@@ -8939,44 +8943,44 @@
         <v>3</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G212" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H212" t="s">
         <v>6</v>
       </c>
       <c r="I212" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B213" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C213" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G213" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H213" t="s">
         <v>6</v>
       </c>
       <c r="I213" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B214" s="10"/>
       <c r="C214" s="10"/>
@@ -8986,13 +8990,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B215" t="s">
         <v>28</v>
       </c>
       <c r="C215" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D215">
         <v>1</v>
@@ -9004,10 +9008,10 @@
         <v>29</v>
       </c>
       <c r="G215" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H215" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I215" t="s">
         <v>1</v>
@@ -9015,13 +9019,13 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B216">
         <v>0</v>
       </c>
       <c r="C216" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D216">
         <v>0</v>
@@ -9033,10 +9037,10 @@
         <v>29</v>
       </c>
       <c r="G216" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H216" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I216" t="s">
         <v>1</v>
@@ -9044,22 +9048,22 @@
     </row>
     <row r="217" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>370</v>
+      </c>
+      <c r="B217" t="s">
+        <v>371</v>
+      </c>
+      <c r="C217" t="s">
+        <v>148</v>
+      </c>
+      <c r="F217" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B217" t="s">
-        <v>373</v>
-      </c>
-      <c r="C217" t="s">
-        <v>150</v>
-      </c>
-      <c r="F217" s="7" t="s">
-        <v>374</v>
-      </c>
       <c r="G217" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H217" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I217" t="s">
         <v>11</v>
@@ -9067,13 +9071,13 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B218" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C218" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D218">
         <v>2</v>
@@ -9085,10 +9089,10 @@
         <v>29</v>
       </c>
       <c r="G218" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H218" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I218" t="s">
         <v>1</v>
@@ -9096,13 +9100,13 @@
     </row>
     <row r="219" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B219" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C219" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D219">
         <v>1</v>
@@ -9111,27 +9115,27 @@
         <v>1</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="G219" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H219" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I219" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B220" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C220" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D220">
         <v>2</v>
@@ -9140,13 +9144,13 @@
         <v>2</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G220" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H220" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I220" t="s">
         <v>1</v>
@@ -9154,13 +9158,13 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>35</v>
+      </c>
+      <c r="B221" t="s">
         <v>36</v>
       </c>
-      <c r="B221" t="s">
-        <v>37</v>
-      </c>
       <c r="C221" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -9169,13 +9173,13 @@
         <v>1</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G221" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H221" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I221" t="s">
         <v>1</v>
@@ -9183,13 +9187,13 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B222" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C222" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D222">
         <v>2</v>
@@ -9198,13 +9202,13 @@
         <v>2</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G222" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H222" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I222" t="s">
         <v>1</v>
@@ -9212,28 +9216,28 @@
     </row>
     <row r="223" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>71</v>
+      </c>
+      <c r="B223" t="s">
+        <v>37</v>
+      </c>
+      <c r="C223" t="s">
+        <v>59</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
+      <c r="F223" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B223" t="s">
-        <v>38</v>
-      </c>
-      <c r="C223" t="s">
-        <v>60</v>
-      </c>
-      <c r="D223">
-        <v>1</v>
-      </c>
-      <c r="E223">
-        <v>1</v>
-      </c>
-      <c r="F223" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="G223" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H223" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I223" t="s">
         <v>1</v>
@@ -9241,13 +9245,13 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B224" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C224" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D224">
         <v>2</v>
@@ -9256,13 +9260,13 @@
         <v>2</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G224" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H224" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I224" t="s">
         <v>4</v>
@@ -9270,13 +9274,13 @@
     </row>
     <row r="225" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>573</v>
+      </c>
+      <c r="B225" t="s">
+        <v>574</v>
+      </c>
+      <c r="C225" t="s">
         <v>575</v>
-      </c>
-      <c r="B225" t="s">
-        <v>576</v>
-      </c>
-      <c r="C225" t="s">
-        <v>577</v>
       </c>
       <c r="D225">
         <v>4</v>
@@ -9285,13 +9289,13 @@
         <v>4</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G225" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H225" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I225" t="s">
         <v>3</v>
@@ -9299,65 +9303,65 @@
     </row>
     <row r="226" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B226">
         <v>3</v>
       </c>
       <c r="C226" t="s">
+        <v>570</v>
+      </c>
+      <c r="D226" t="s">
+        <v>554</v>
+      </c>
+      <c r="E226" t="s">
+        <v>554</v>
+      </c>
+      <c r="F226" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="D226" t="s">
-        <v>556</v>
-      </c>
-      <c r="E226" t="s">
-        <v>556</v>
-      </c>
-      <c r="F226" s="7" t="s">
-        <v>574</v>
-      </c>
       <c r="G226" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H226" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I226" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>491</v>
+      </c>
+      <c r="B227" t="s">
+        <v>492</v>
+      </c>
+      <c r="C227" t="s">
+        <v>206</v>
+      </c>
+      <c r="F227" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="B227" t="s">
-        <v>494</v>
-      </c>
-      <c r="C227" t="s">
-        <v>208</v>
-      </c>
-      <c r="F227" s="7" t="s">
-        <v>495</v>
-      </c>
       <c r="G227" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H227" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I227" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B228" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C228" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D228">
         <v>2</v>
@@ -9366,13 +9370,13 @@
         <v>2</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G228" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H228" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I228" t="s">
         <v>1</v>
@@ -9380,7 +9384,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B229" s="13"/>
       <c r="C229" s="13"/>
@@ -9390,13 +9394,13 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B230">
         <v>2</v>
       </c>
       <c r="C230" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D230">
         <v>2</v>
@@ -9405,86 +9409,86 @@
         <v>2</v>
       </c>
       <c r="G230" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H230" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C231" t="s">
+        <v>150</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G231" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H231" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="F231" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G231" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H231" s="7" t="s">
-        <v>154</v>
       </c>
       <c r="I231" s="7"/>
       <c r="J231" s="7"/>
     </row>
     <row r="232" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G232" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H232" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C233" t="s">
+        <v>150</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G233" t="s">
+        <v>90</v>
+      </c>
+      <c r="H233" t="s">
         <v>152</v>
-      </c>
-      <c r="F233" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="G233" t="s">
-        <v>92</v>
-      </c>
-      <c r="H233" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B234">
         <v>3</v>
       </c>
       <c r="C234" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G234" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H234" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I234" t="s">
         <v>3</v>
@@ -9492,13 +9496,13 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D235">
         <v>0</v>
@@ -9507,13 +9511,13 @@
         <v>1</v>
       </c>
       <c r="F235" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G235" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H235" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I235" t="s">
         <v>3</v>
@@ -9521,22 +9525,22 @@
     </row>
     <row r="236" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B236">
         <v>3</v>
       </c>
       <c r="C236" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F236" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G236" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H236" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I236" t="s">
         <v>0</v>
@@ -9544,22 +9548,22 @@
     </row>
     <row r="237" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B237">
         <v>3</v>
       </c>
       <c r="C237" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G237" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H237" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I237" t="s">
         <v>0</v>
@@ -9567,22 +9571,22 @@
     </row>
     <row r="238" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B238">
         <v>3</v>
       </c>
       <c r="C238" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G238" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H238" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I238" t="s">
         <v>0</v>
@@ -9590,22 +9594,22 @@
     </row>
     <row r="239" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B239">
         <v>2</v>
       </c>
       <c r="C239" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G239" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H239" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I239" t="s">
         <v>0</v>
@@ -9613,42 +9617,42 @@
     </row>
     <row r="240" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B240">
         <v>2</v>
       </c>
       <c r="C240" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F240" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G240" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H240" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B241">
         <v>1</v>
       </c>
       <c r="C241" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F241" s="7" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G241" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H241" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I241" t="s">
         <v>11</v>
@@ -9656,13 +9660,13 @@
     </row>
     <row r="242" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B242">
         <v>2</v>
       </c>
       <c r="C242" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -9671,24 +9675,24 @@
         <v>1</v>
       </c>
       <c r="F242" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G242" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H242" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B243">
         <v>2</v>
       </c>
       <c r="C243" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D243">
         <v>1</v>
@@ -9697,13 +9701,13 @@
         <v>1</v>
       </c>
       <c r="F243" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G243" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H243" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I243" t="s">
         <v>3</v>
@@ -9711,22 +9715,22 @@
     </row>
     <row r="244" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B244">
         <v>1</v>
       </c>
       <c r="C244" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G244" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H244" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I244" t="s">
         <v>11</v>
@@ -9734,42 +9738,42 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B245">
         <v>3</v>
       </c>
       <c r="C245" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F245" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G245" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H245" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="246" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B246">
         <v>5</v>
       </c>
       <c r="C246" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F246" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G246" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H246" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I246" t="s">
         <v>4</v>
@@ -9777,36 +9781,36 @@
     </row>
     <row r="247" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C247" t="s">
+        <v>150</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="G247" t="s">
+        <v>92</v>
+      </c>
+      <c r="H247" t="s">
         <v>152</v>
-      </c>
-      <c r="F247" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="G247" t="s">
-        <v>94</v>
-      </c>
-      <c r="H247" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C248" t="s">
+        <v>150</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="G248" t="s">
+        <v>92</v>
+      </c>
+      <c r="H248" t="s">
         <v>152</v>
-      </c>
-      <c r="F248" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="G248" t="s">
-        <v>94</v>
-      </c>
-      <c r="H248" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/btd mtg.xlsx
+++ b/btd mtg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Nicholas\Documents\wargame\wargame-tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5A2919-5E18-4012-9418-5258AADB5C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994F0F68-4CF0-4699-AC99-38CFE07FA8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{0FBAB4E1-BC52-3645-BE0D-36FD61AE4D11}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Cycles" sheetId="3" r:id="rId2"/>
     <sheet name="Card list" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="706">
   <si>
     <t>Hive Courts</t>
   </si>
@@ -2101,6 +2102,66 @@
   </si>
   <si>
     <t>~ CITP with 5 +1/+1 counters</t>
+  </si>
+  <si>
+    <t>POST PRINT additions</t>
+  </si>
+  <si>
+    <t>Notes post printing</t>
+  </si>
+  <si>
+    <t>Add more clerics. There is almost no support. Maybe a CUR cycle in URB</t>
+  </si>
+  <si>
+    <t>More larger chaff for draft in general 4/4+</t>
+  </si>
+  <si>
+    <t>Spore Harvester</t>
+  </si>
+  <si>
+    <t>Herculean Vanguard</t>
+  </si>
+  <si>
+    <t>Unstable Mass</t>
+  </si>
+  <si>
+    <t>Fleshcraft 2U; When Unstable Mass is targeted by a spell or ability an opponent controls, you may remove a creature fleshcrafted onto it. If you do, counter that spell or ability.</t>
+  </si>
+  <si>
+    <t>T: Regenerate target non-Cleric Human.</t>
+  </si>
+  <si>
+    <t>Flesh Mender</t>
+  </si>
+  <si>
+    <t>Deformation Mage</t>
+  </si>
+  <si>
+    <t>T: Give up to X creatures -1/-0 until the end of the turn, where X is the number of lands you control.</t>
+  </si>
+  <si>
+    <t>Cackling Archivist</t>
+  </si>
+  <si>
+    <t>When a creature you control fleshcrafts, draw a card</t>
+  </si>
+  <si>
+    <t>Spore Harvester gets +1/+1 for each -1/-1 counter on all creatures.</t>
+  </si>
+  <si>
+    <t>Sacrifice a non-Cleric Human: Each opponent loses X life and you gain X life, where X is the sum of the creature's power and toughness.</t>
+  </si>
+  <si>
+    <t>Demented Ritualist</t>
+  </si>
+  <si>
+    <t>Maestro Basil</t>
+  </si>
+  <si>
+    <t>2(2/R)U</t>
+  </si>
+  <si>
+    <t>T, put a fleshcrafted creature attached to target creature onto the bottom of your library.  If you do, reveal cards from the top of your library until you reveal a non-Cleric Human.  Fleshcraft the chosen card onto the targeted creature.</t>
   </si>
 </sst>
 </file>
@@ -3236,7 +3297,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90AA90A0-4951-4ECF-AE6C-D6938F4AC6B5}">
-  <dimension ref="A1:X248"/>
+  <dimension ref="A1:X264"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.625" bestFit="1" customWidth="1"/>
@@ -3278,35 +3339,35 @@
       </c>
       <c r="J1">
         <f>SUM(L1,N1,P1,R1,T1,V1,X1)</f>
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K1" s="14" t="s">
         <v>116</v>
       </c>
       <c r="L1" s="15">
         <f>COUNTIF($H:$H,"White")</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M1" s="15" t="s">
         <v>117</v>
       </c>
       <c r="N1" s="15">
         <f>COUNTIF($H:$H,"Black")</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O1" s="15" t="s">
         <v>118</v>
       </c>
       <c r="P1" s="15">
         <f>COUNTIF($H:$H,"Blue")</f>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>119</v>
       </c>
       <c r="R1" s="15">
         <f>COUNTIF($H:$H,"Red")</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S1" s="15" t="s">
         <v>120</v>
@@ -3350,7 +3411,7 @@
       </c>
       <c r="P2">
         <f>COUNTIF($I:$I,O2)</f>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
         <v>145</v>
@@ -3395,21 +3456,21 @@
       </c>
       <c r="L3" s="20">
         <f>COUNTIF($G:$G,K3)</f>
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="M3" s="20" t="s">
         <v>91</v>
       </c>
       <c r="N3" s="20">
         <f>COUNTIF($G:$G,M3)</f>
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="O3" s="20" t="s">
         <v>92</v>
       </c>
       <c r="P3" s="20">
         <f>COUNTIF($G:$G,O3)</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
@@ -3453,7 +3514,7 @@
       </c>
       <c r="L4" s="20">
         <f>COUNTIF($C:$C,"*Creature*")</f>
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="M4" s="19" t="s">
         <v>148</v>
@@ -9811,6 +9872,293 @@
       </c>
       <c r="H248" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>690</v>
+      </c>
+      <c r="B253" t="s">
+        <v>182</v>
+      </c>
+      <c r="C253" t="s">
+        <v>59</v>
+      </c>
+      <c r="D253">
+        <v>3</v>
+      </c>
+      <c r="E253">
+        <v>3</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="G253" t="s">
+        <v>91</v>
+      </c>
+      <c r="H253" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>691</v>
+      </c>
+      <c r="B254" t="s">
+        <v>94</v>
+      </c>
+      <c r="C254" t="s">
+        <v>129</v>
+      </c>
+      <c r="D254">
+        <v>6</v>
+      </c>
+      <c r="E254">
+        <v>6</v>
+      </c>
+      <c r="F254" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="G254" t="s">
+        <v>90</v>
+      </c>
+      <c r="H254" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>692</v>
+      </c>
+      <c r="B255" t="s">
+        <v>91</v>
+      </c>
+      <c r="C255" t="s">
+        <v>344</v>
+      </c>
+      <c r="D255">
+        <v>1</v>
+      </c>
+      <c r="E255">
+        <v>1</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="G255" t="s">
+        <v>90</v>
+      </c>
+      <c r="H255" t="s">
+        <v>8</v>
+      </c>
+      <c r="I255" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>696</v>
+      </c>
+      <c r="B256" t="s">
+        <v>91</v>
+      </c>
+      <c r="C256" t="s">
+        <v>408</v>
+      </c>
+      <c r="D256">
+        <v>1</v>
+      </c>
+      <c r="E256">
+        <v>2</v>
+      </c>
+      <c r="F256" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="G256" t="s">
+        <v>90</v>
+      </c>
+      <c r="H256" t="s">
+        <v>8</v>
+      </c>
+      <c r="I256" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>698</v>
+      </c>
+      <c r="B257" t="s">
+        <v>194</v>
+      </c>
+      <c r="C257" t="s">
+        <v>408</v>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+      <c r="E257">
+        <v>4</v>
+      </c>
+      <c r="F257" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="G257" t="s">
+        <v>91</v>
+      </c>
+      <c r="H257" t="s">
+        <v>8</v>
+      </c>
+      <c r="I257" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>703</v>
+      </c>
+      <c r="B258" t="s">
+        <v>704</v>
+      </c>
+      <c r="C258" t="s">
+        <v>408</v>
+      </c>
+      <c r="D258">
+        <v>3</v>
+      </c>
+      <c r="E258">
+        <v>3</v>
+      </c>
+      <c r="F258" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="G258" t="s">
+        <v>92</v>
+      </c>
+      <c r="H258" t="s">
+        <v>8</v>
+      </c>
+      <c r="I258" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>695</v>
+      </c>
+      <c r="B259" t="s">
+        <v>194</v>
+      </c>
+      <c r="C259" t="s">
+        <v>408</v>
+      </c>
+      <c r="D259">
+        <v>2</v>
+      </c>
+      <c r="E259">
+        <v>2</v>
+      </c>
+      <c r="F259" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="G259" t="s">
+        <v>90</v>
+      </c>
+      <c r="H259" t="s">
+        <v>9</v>
+      </c>
+      <c r="I259" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>702</v>
+      </c>
+      <c r="B260" t="s">
+        <v>274</v>
+      </c>
+      <c r="C260" t="s">
+        <v>408</v>
+      </c>
+      <c r="D260">
+        <v>3</v>
+      </c>
+      <c r="E260">
+        <v>4</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="G260" t="s">
+        <v>91</v>
+      </c>
+      <c r="H260" t="s">
+        <v>9</v>
+      </c>
+      <c r="I260" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C261" t="s">
+        <v>408</v>
+      </c>
+      <c r="G261" t="s">
+        <v>92</v>
+      </c>
+      <c r="H261" t="s">
+        <v>9</v>
+      </c>
+      <c r="I261" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C262" t="s">
+        <v>408</v>
+      </c>
+      <c r="G262" t="s">
+        <v>90</v>
+      </c>
+      <c r="H262" t="s">
+        <v>6</v>
+      </c>
+      <c r="I262" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C263" t="s">
+        <v>408</v>
+      </c>
+      <c r="G263" t="s">
+        <v>91</v>
+      </c>
+      <c r="H263" t="s">
+        <v>6</v>
+      </c>
+      <c r="I263" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C264" t="s">
+        <v>408</v>
+      </c>
+      <c r="G264" t="s">
+        <v>92</v>
+      </c>
+      <c r="H264" t="s">
+        <v>6</v>
+      </c>
+      <c r="I264" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9820,4 +10168,32 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3298D37-1E74-4139-9058-B1C1A29F9886}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="60.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>